--- a/data/trans_orig/IP32-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9177</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39330</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47797</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48322</t>
+          <t>47731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56697</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91335</t>
+          <t>90958</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102284</t>
+          <t>102362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92166</t>
+          <t>91443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98492</t>
+          <t>98502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94900</t>
+          <t>94445</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>104203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189941</t>
+          <t>190412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201354</t>
+          <t>201191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58899</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65518</t>
+          <t>65483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59708</t>
+          <t>60220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67195</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122439</t>
+          <t>122524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>131747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>63307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71472</t>
+          <t>71651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>63635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129588</t>
+          <t>130164</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>142578</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>33099</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>39868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>42073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70303</t>
+          <t>69800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>80460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105771</t>
+          <t>105424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113248</t>
+          <t>113175</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>9686</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>40320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96847</t>
+          <t>96454</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110704</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102308</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>117163</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>203940</t>
+          <t>203301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>225079</t>
+          <t>224264</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>142776</t>
+          <t>142579</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>152588</t>
+          <t>152436</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>146054</t>
+          <t>147348</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>157032</t>
+          <t>157405</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>293335</t>
+          <t>292531</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>307135</t>
+          <t>307484</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>53586</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>78284</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>61271</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>87207</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>602637</t>
+          <t>601674</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>625959</t>
+          <t>626517</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>632812</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>659522</t>
+          <t>658334</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1242459</t>
+          <t>1243199</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1278423</t>
+          <t>1278122</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>42828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53308</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>52374</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61941</t>
+          <t>61645</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>100586</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113098</t>
+          <t>113253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94159</t>
+          <t>95116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102459</t>
+          <t>103103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101528</t>
+          <t>101484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109839</t>
+          <t>109852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200252</t>
+          <t>200374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211305</t>
+          <t>211048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5526</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61490</t>
+          <t>61166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67525</t>
+          <t>67520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65119</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129780</t>
+          <t>129328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137786</t>
+          <t>137784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9138</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>64618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73997</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71538</t>
+          <t>70701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>80373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139738</t>
+          <t>139651</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152386</t>
+          <t>152728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43714</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87437</t>
+          <t>86411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55262</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>51187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59121</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>103597</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113624</t>
+          <t>113663</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>124696</t>
+          <t>124400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>134897</t>
+          <t>134765</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>125486</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>138313</t>
+          <t>138524</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>254179</t>
+          <t>253652</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>270925</t>
+          <t>270237</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>156241</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>163276</t>
+          <t>163272</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>162281</t>
+          <t>161625</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>170004</t>
+          <t>170033</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>321763</t>
+          <t>321669</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>332147</t>
+          <t>331806</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69352</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>661289</t>
+          <t>661036</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>683636</t>
+          <t>682673</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>700794</t>
+          <t>701929</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>723993</t>
+          <t>724527</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1369732</t>
+          <t>1371707</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1402025</t>
+          <t>1403888</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>487</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56037</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54104</t>
+          <t>53564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62368</t>
+          <t>62499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106220</t>
+          <t>106172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117306</t>
+          <t>116860</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94768</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>102517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205692</t>
+          <t>205156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212697</t>
+          <t>212761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>60878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>65596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130587</t>
+          <t>130034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>63805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73629</t>
+          <t>73344</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68969</t>
+          <t>68529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78459</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137308</t>
+          <t>136019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149962</t>
+          <t>149987</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>39735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45786</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80813</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88302</t>
+          <t>88579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>47068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53566</t>
+          <t>53309</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104608</t>
+          <t>104701</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111354</t>
+          <t>111359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>130491</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136740</t>
+          <t>136749</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>134914</t>
+          <t>134410</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142064</t>
+          <t>142059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>269006</t>
+          <t>268817</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>277814</t>
+          <t>277919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>153681</t>
+          <t>153905</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>161918</t>
+          <t>161492</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>163396</t>
+          <t>164301</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>170174</t>
+          <t>170182</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>320978</t>
+          <t>320217</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>330340</t>
+          <t>330419</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>665699</t>
+          <t>665910</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>684384</t>
+          <t>683685</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>713216</t>
+          <t>713081</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>730234</t>
+          <t>729719</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1384679</t>
+          <t>1384601</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1411031</t>
+          <t>1409256</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66915</t>
+          <t>65649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73707</t>
+          <t>73876</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>144411</t>
+          <t>144004</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152031</t>
+          <t>151965</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118564</t>
+          <t>118804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124721</t>
+          <t>124854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120732</t>
+          <t>120487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127060</t>
+          <t>126971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242897</t>
+          <t>242691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250968</t>
+          <t>251043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52662</t>
+          <t>52516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57648</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63207</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>118992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124805</t>
+          <t>124632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>327</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61875</t>
+          <t>62145</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69654</t>
+          <t>69663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77695</t>
+          <t>77722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137597</t>
+          <t>137274</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>146097</t>
+          <t>146420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31050</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39852</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67936</t>
+          <t>68114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73308</t>
+          <t>73485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>55855</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98627</t>
+          <t>98666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>102009</t>
+          <t>102016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105030</t>
+          <t>105105</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121098</t>
+          <t>120983</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>122607</t>
+          <t>121513</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151408</t>
+          <t>151252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>240875</t>
+          <t>241430</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>270077</t>
+          <t>269857</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>125576</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131119</t>
+          <t>130973</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>145116</t>
+          <t>144532</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>155587</t>
+          <t>155635</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>274149</t>
+          <t>274515</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>285819</t>
+          <t>285691</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42390</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>629554</t>
+          <t>630853</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>650883</t>
+          <t>650820</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>715563</t>
+          <t>714587</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>745770</t>
+          <t>745205</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1354823</t>
+          <t>1357004</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1391371</t>
+          <t>1391987</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
